--- a/Result/profitability/6526.xlsx
+++ b/Result/profitability/6526.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM27"/>
+  <dimension ref="A1:AM28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,6 +3859,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6526</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6289</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3071</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3217</v>
+      </c>
+      <c r="F28" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="G28" t="n">
+        <v>943</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>84</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1027</v>
+      </c>
+      <c r="K28" t="n">
+        <v>880</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.484999999999999</v>
+      </c>
+      <c r="N28" t="n">
+        <v>52.01125</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.7800000000000002</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.174496644295302</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-0.0297743220178267</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.6100000000000003</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.1314655172413794</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.6699999999999946</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.01326995444642498</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
